--- a/content/actions.xlsx
+++ b/content/actions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -22,9 +22,15 @@
     <t>category</t>
   </si>
   <si>
+    <t>categoryName</t>
+  </si>
+  <si>
     <t>stat</t>
   </si>
   <si>
+    <t>statName</t>
+  </si>
+  <si>
     <t>stamina</t>
   </si>
   <si>
@@ -52,9 +58,15 @@
     <t>growth</t>
   </si>
   <si>
+    <t>提升属性</t>
+  </si>
+  <si>
     <t>vocal</t>
   </si>
   <si>
+    <t>演唱</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -70,6 +82,9 @@
     <t>dance</t>
   </si>
   <si>
+    <t>舞蹈</t>
+  </si>
+  <si>
     <t>对着镜子把同一段副歌跳了二十遍。（舞蹈 +{n}）</t>
   </si>
   <si>
@@ -82,6 +97,9 @@
     <t>acting</t>
   </si>
   <si>
+    <t>演技</t>
+  </si>
+  <si>
     <t>自导自演拍了三条，第二条最好。（演技 +{n}）</t>
   </si>
   <si>
@@ -94,6 +112,9 @@
     <t>talk</t>
   </si>
   <si>
+    <t>口才</t>
+  </si>
+  <si>
     <t>对着镜头练了一下午串场词。（口才 +{n}）</t>
   </si>
   <si>
@@ -106,6 +127,9 @@
     <t>work</t>
   </si>
   <si>
+    <t>赚钱</t>
+  </si>
+  <si>
     <t>在便利店站了四个小时，脚有点麻。（收入 +320）</t>
   </si>
   <si>
@@ -116,6 +140,9 @@
   </si>
   <si>
     <t>recover</t>
+  </si>
+  <si>
+    <t>恢复状态</t>
   </si>
   <si>
     <t>睡了一觉，感觉活过来了。</t>
@@ -504,20 +531,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="9" width="24" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,197 +577,239 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2">
         <v>-10</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>50</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>-12</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>-12</v>
-      </c>
-      <c r="F3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>-10</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5">
+        <v>-8</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4">
-        <v>-10</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>-20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6">
+        <v>320</v>
+      </c>
+      <c r="L6" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5">
-        <v>-8</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>-20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>320</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/content/actions.xlsx
+++ b/content/actions.xlsx
@@ -11,42 +11,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>categoryName</t>
-  </si>
-  <si>
-    <t>stat</t>
-  </si>
-  <si>
-    <t>statName</t>
-  </si>
-  <si>
-    <t>stamina</t>
-  </si>
-  <si>
-    <t>gainMin</t>
-  </si>
-  <si>
-    <t>gainMax</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>money</t>
-  </si>
-  <si>
-    <t>text</t>
+    <t>行为名称</t>
+  </si>
+  <si>
+    <t>行为分类</t>
+  </si>
+  <si>
+    <t>分类字段名</t>
+  </si>
+  <si>
+    <t>显示条件</t>
+  </si>
+  <si>
+    <t>次数</t>
+  </si>
+  <si>
+    <t>次数范围</t>
+  </si>
+  <si>
+    <t>影响属性</t>
+  </si>
+  <si>
+    <t>单次分钟</t>
   </si>
   <si>
     <t>vocal-karaoke</t>
@@ -55,24 +46,21 @@
     <t>唱 K</t>
   </si>
   <si>
+    <t>提升属性</t>
+  </si>
+  <si>
     <t>growth</t>
   </si>
   <si>
-    <t>提升属性</t>
+    <t/>
+  </si>
+  <si>
+    <t>run</t>
   </si>
   <si>
     <t>vocal</t>
   </si>
   <si>
-    <t>演唱</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>你在包厢里唱了两小时，嗓子有点热。（演唱 +{n}）</t>
-  </si>
-  <si>
     <t>dance-otaku</t>
   </si>
   <si>
@@ -82,12 +70,6 @@
     <t>dance</t>
   </si>
   <si>
-    <t>舞蹈</t>
-  </si>
-  <si>
-    <t>对着镜子把同一段副歌跳了二十遍。（舞蹈 +{n}）</t>
-  </si>
-  <si>
     <t>acting-short</t>
   </si>
   <si>
@@ -97,12 +79,6 @@
     <t>acting</t>
   </si>
   <si>
-    <t>演技</t>
-  </si>
-  <si>
-    <t>自导自演拍了三条，第二条最好。（演技 +{n}）</t>
-  </si>
-  <si>
     <t>talk-selftalk</t>
   </si>
   <si>
@@ -112,40 +88,28 @@
     <t>talk</t>
   </si>
   <si>
-    <t>口才</t>
-  </si>
-  <si>
-    <t>对着镜头练了一下午串场词。（口才 +{n}）</t>
-  </si>
-  <si>
     <t>work-part-time</t>
   </si>
   <si>
     <t>打工</t>
   </si>
   <si>
+    <t>赚钱</t>
+  </si>
+  <si>
     <t>work</t>
   </si>
   <si>
-    <t>赚钱</t>
-  </si>
-  <si>
-    <t>在便利店站了四个小时，脚有点麻。（收入 +320）</t>
-  </si>
-  <si>
     <t>rest-sleep</t>
   </si>
   <si>
     <t>爆睡</t>
   </si>
   <si>
+    <t>恢复状态</t>
+  </si>
+  <si>
     <t>recover</t>
-  </si>
-  <si>
-    <t>恢复状态</t>
-  </si>
-  <si>
-    <t>睡了一觉，感觉活过来了。</t>
   </si>
 </sst>
 </file>
@@ -531,22 +495,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,242 +534,179 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2">
-        <v>-10</v>
-      </c>
-      <c r="H2">
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>50</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3">
-        <v>-12</v>
-      </c>
-      <c r="H3">
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4">
-        <v>-10</v>
-      </c>
-      <c r="H4">
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5">
-        <v>-8</v>
-      </c>
-      <c r="H5">
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7">
         <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>-20</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6">
-        <v>320</v>
-      </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/content/actions.xlsx
+++ b/content/actions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -110,6 +110,24 @@
   </si>
   <si>
     <t>recover</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>演出</t>
+  </si>
+  <si>
+    <t>performance</t>
+  </si>
+  <si>
+    <t>{"statsSumAtLeast":60}</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>vocal,dance,acting,talk</t>
   </si>
 </sst>
 </file>
@@ -495,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -709,6 +727,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
